--- a/public/magnets/goal-planner.xlsx
+++ b/public/magnets/goal-planner.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₦&quot;#,##0;[Red]-&quot;₦&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.##"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     </font>
     <font>
       <color rgb="004C6A62"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="009AA8A3"/>
     </font>
     <font>
       <b val="1"/>
@@ -124,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,30 +147,49 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="00000000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -528,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B34"/>
+  <dimension ref="B1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -629,82 +652,96 @@
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Only type in the yellow cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
+          <t>The gray words in yellow cells are hints</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>The white cells hold formulas that do the maths. If you type over one by mistake, download a fresh copy.</t>
+          <t>Each yellow cell shows a gray hint such as "e.g. 250,000". It is only a hint: it doesn't count. Tap the cell and type your own number over it; your number turns black and the totals update. Leave the hint in any cell that doesn't apply to you. Tap a cell to see a short instruction for it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Want to see a finished one first?</t>
+          <t>Only type in the yellow cells</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Open the "Example" tab: Esther's goals, from her emergency fund to her children's university. Don't type your own goals there.</t>
+          <t>The white cells hold formulas that do the maths. If you type over one by mistake, download a fresh copy.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>These are estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>Want to see a finished one first?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The sheet assumes prices rise by the same percentage every year. Real prices don't move that neatly, which is why you check once a year. It doesn't count any interest your savings earn, so the monthly amounts are on the safe side.</t>
+          <t>Open the "Example" tab: Esther's goals, from her emergency fund to her children's university. Don't type your own goals there.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>On a phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
+          <t>These are estimates</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Open the file with the free Google Sheets or Microsoft Excel app. In Google Sheets, tap File &gt; Make a copy (or Save as Google Sheets) so you can edit it and keep it.</t>
+          <t>The sheet assumes prices rise by the same percentage every year. Real prices don't move that neatly, which is why you check once a year. It doesn't count any interest your savings earn, so the monthly amounts are on the safe side.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>On a phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Open the file with the free Google Sheets or Microsoft Excel app. In Google Sheets, tap File &gt; Make a copy (or Save as Google Sheets) so you can edit it and keep it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>Your privacy</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>This file stays on your phone or computer. Nobody else sees your goals or numbers.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="4" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>From the free Financial Intelligence class: kopkad.ng/blog. For educational purposes only. This is not financial advice.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>With Snowball, we keep it rolling.</t>
         </is>
@@ -788,7 +825,11 @@
           <t>What I can save each month</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>e.g. 160,000</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Your monthly surplus from your Money Map (money in − money out).</t>
@@ -853,310 +894,342 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="15">
-        <f>IF(E9="","",IF(F9="Yes",E9+G9,(E9*(1+$C$4)^C9+G9)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="15">
-        <f>IF(I9="","",MAX(0,I9-H9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
-        <f>IF(OR(J9="",C9=""),"",IF(C9&lt;=0,J9,J9/(C9*12)))</f>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>e.g. Rent</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>choose ▾</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>e.g. 0.5</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>e.g. 1</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>e.g. 600,000</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>choose ▾</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>e.g. 0</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>e.g. 120,000</t>
+        </is>
+      </c>
+      <c r="I9" s="16">
+        <f>IF(NOT(ISNUMBER(E9)),"",IF(F9="Yes",E9+N(G9),(E9*(1+$C$4)^N(C9)+N(G9))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="16">
+        <f>IF(I9="","",MAX(0,I9-N(H9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>IF(OR(J9="",NOT(ISNUMBER(C9))),"",IF(C9&lt;=0,J9,J9/(C9*12)))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="14" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="15">
-        <f>IF(E10="","",IF(F10="Yes",E10+G10,(E10*(1+$C$4)^C10+G10)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="15">
-        <f>IF(I10="","",MAX(0,I10-H10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="16">
-        <f>IF(OR(J10="",C10=""),"",IF(C10&lt;=0,J10,J10/(C10*12)))</f>
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="13" t="inlineStr"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="13" t="inlineStr"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="16">
+        <f>IF(NOT(ISNUMBER(E10)),"",IF(F10="Yes",E10+N(G10),(E10*(1+$C$4)^N(C10)+N(G10))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="16">
+        <f>IF(I10="","",MAX(0,I10-N(H10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>IF(OR(J10="",NOT(ISNUMBER(C10))),"",IF(C10&lt;=0,J10,J10/(C10*12)))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="10" t="n"/>
-      <c r="F11" s="14" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="15">
-        <f>IF(E11="","",IF(F11="Yes",E11+G11,(E11*(1+$C$4)^C11+G11)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="15">
-        <f>IF(I11="","",MAX(0,I11-H11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="16">
-        <f>IF(OR(J11="",C11=""),"",IF(C11&lt;=0,J11,J11/(C11*12)))</f>
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="13" t="inlineStr"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="13" t="inlineStr"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="16">
+        <f>IF(NOT(ISNUMBER(E11)),"",IF(F11="Yes",E11+N(G11),(E11*(1+$C$4)^N(C11)+N(G11))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="16">
+        <f>IF(I11="","",MAX(0,I11-N(H11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>IF(OR(J11="",NOT(ISNUMBER(C11))),"",IF(C11&lt;=0,J11,J11/(C11*12)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="15">
-        <f>IF(E12="","",IF(F12="Yes",E12+G12,(E12*(1+$C$4)^C12+G12)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="15">
-        <f>IF(I12="","",MAX(0,I12-H12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="16">
-        <f>IF(OR(J12="",C12=""),"",IF(C12&lt;=0,J12,J12/(C12*12)))</f>
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="13" t="inlineStr"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="13" t="inlineStr"/>
+      <c r="G12" s="21" t="n"/>
+      <c r="H12" s="21" t="n"/>
+      <c r="I12" s="16">
+        <f>IF(NOT(ISNUMBER(E12)),"",IF(F12="Yes",E12+N(G12),(E12*(1+$C$4)^N(C12)+N(G12))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="16">
+        <f>IF(I12="","",MAX(0,I12-N(H12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="17">
+        <f>IF(OR(J12="",NOT(ISNUMBER(C12))),"",IF(C12&lt;=0,J12,J12/(C12*12)))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="14" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="15">
-        <f>IF(E13="","",IF(F13="Yes",E13+G13,(E13*(1+$C$4)^C13+G13)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="15">
-        <f>IF(I13="","",MAX(0,I13-H13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="16">
-        <f>IF(OR(J13="",C13=""),"",IF(C13&lt;=0,J13,J13/(C13*12)))</f>
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="13" t="inlineStr"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="13" t="inlineStr"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="21" t="n"/>
+      <c r="I13" s="16">
+        <f>IF(NOT(ISNUMBER(E13)),"",IF(F13="Yes",E13+N(G13),(E13*(1+$C$4)^N(C13)+N(G13))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="16">
+        <f>IF(I13="","",MAX(0,I13-N(H13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>IF(OR(J13="",NOT(ISNUMBER(C13))),"",IF(C13&lt;=0,J13,J13/(C13*12)))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="15">
-        <f>IF(E14="","",IF(F14="Yes",E14+G14,(E14*(1+$C$4)^C14+G14)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="15">
-        <f>IF(I14="","",MAX(0,I14-H14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="16">
-        <f>IF(OR(J14="",C14=""),"",IF(C14&lt;=0,J14,J14/(C14*12)))</f>
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="13" t="inlineStr"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="16">
+        <f>IF(NOT(ISNUMBER(E14)),"",IF(F14="Yes",E14+N(G14),(E14*(1+$C$4)^N(C14)+N(G14))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="16">
+        <f>IF(I14="","",MAX(0,I14-N(H14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>IF(OR(J14="",NOT(ISNUMBER(C14))),"",IF(C14&lt;=0,J14,J14/(C14*12)))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="15">
-        <f>IF(E15="","",IF(F15="Yes",E15+G15,(E15*(1+$C$4)^C15+G15)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J15" s="15">
-        <f>IF(I15="","",MAX(0,I15-H15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="16">
-        <f>IF(OR(J15="",C15=""),"",IF(C15&lt;=0,J15,J15/(C15*12)))</f>
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="13" t="inlineStr"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="16">
+        <f>IF(NOT(ISNUMBER(E15)),"",IF(F15="Yes",E15+N(G15),(E15*(1+$C$4)^N(C15)+N(G15))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="16">
+        <f>IF(I15="","",MAX(0,I15-N(H15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>IF(OR(J15="",NOT(ISNUMBER(C15))),"",IF(C15&lt;=0,J15,J15/(C15*12)))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="15">
-        <f>IF(E16="","",IF(F16="Yes",E16+G16,(E16*(1+$C$4)^C16+G16)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="15">
-        <f>IF(I16="","",MAX(0,I16-H16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="16">
-        <f>IF(OR(J16="",C16=""),"",IF(C16&lt;=0,J16,J16/(C16*12)))</f>
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="13" t="inlineStr"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="16">
+        <f>IF(NOT(ISNUMBER(E16)),"",IF(F16="Yes",E16+N(G16),(E16*(1+$C$4)^N(C16)+N(G16))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="16">
+        <f>IF(I16="","",MAX(0,I16-N(H16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>IF(OR(J16="",NOT(ISNUMBER(C16))),"",IF(C16&lt;=0,J16,J16/(C16*12)))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="15">
-        <f>IF(E17="","",IF(F17="Yes",E17+G17,(E17*(1+$C$4)^C17+G17)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="15">
-        <f>IF(I17="","",MAX(0,I17-H17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="16">
-        <f>IF(OR(J17="",C17=""),"",IF(C17&lt;=0,J17,J17/(C17*12)))</f>
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="16">
+        <f>IF(NOT(ISNUMBER(E17)),"",IF(F17="Yes",E17+N(G17),(E17*(1+$C$4)^N(C17)+N(G17))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="16">
+        <f>IF(I17="","",MAX(0,I17-N(H17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>IF(OR(J17="",NOT(ISNUMBER(C17))),"",IF(C17&lt;=0,J17,J17/(C17*12)))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="15">
-        <f>IF(E18="","",IF(F18="Yes",E18+G18,(E18*(1+$C$4)^C18+G18)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15">
-        <f>IF(I18="","",MAX(0,I18-H18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="16">
-        <f>IF(OR(J18="",C18=""),"",IF(C18&lt;=0,J18,J18/(C18*12)))</f>
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="13" t="inlineStr"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="16">
+        <f>IF(NOT(ISNUMBER(E18)),"",IF(F18="Yes",E18+N(G18),(E18*(1+$C$4)^N(C18)+N(G18))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>IF(I18="","",MAX(0,I18-N(H18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF(OR(J18="",NOT(ISNUMBER(C18))),"",IF(C18&lt;=0,J18,J18/(C18*12)))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="15">
-        <f>IF(E19="","",IF(F19="Yes",E19+G19,(E19*(1+$C$4)^C19+G19)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J19" s="15">
-        <f>IF(I19="","",MAX(0,I19-H19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="16">
-        <f>IF(OR(J19="",C19=""),"",IF(C19&lt;=0,J19,J19/(C19*12)))</f>
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="13" t="inlineStr"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="13" t="inlineStr"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="16">
+        <f>IF(NOT(ISNUMBER(E19)),"",IF(F19="Yes",E19+N(G19),(E19*(1+$C$4)^N(C19)+N(G19))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="16">
+        <f>IF(I19="","",MAX(0,I19-N(H19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>IF(OR(J19="",NOT(ISNUMBER(C19))),"",IF(C19&lt;=0,J19,J19/(C19*12)))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="15">
-        <f>IF(E20="","",IF(F20="Yes",E20+G20,(E20*(1+$C$4)^C20+G20)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J20" s="15">
-        <f>IF(I20="","",MAX(0,I20-H20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="16">
-        <f>IF(OR(J20="",C20=""),"",IF(C20&lt;=0,J20,J20/(C20*12)))</f>
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="13" t="inlineStr"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="13" t="inlineStr"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="16">
+        <f>IF(NOT(ISNUMBER(E20)),"",IF(F20="Yes",E20+N(G20),(E20*(1+$C$4)^N(C20)+N(G20))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IF(I20="","",MAX(0,I20-N(H20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>IF(OR(J20="",NOT(ISNUMBER(C20))),"",IF(C20&lt;=0,J20,J20/(C20*12)))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Total needed each month for all goals</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="19">
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="24">
         <f>SUM(K9:K20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Can I afford all of them?</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>If "Not yet": give each goal a priority, fund the top ones first, move a date later, or start smaller.</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="17">
-        <f>IF($C$6="","Fill in C6",IF(K22&lt;=$C$6,"Yes","Not yet"))</f>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="22">
+        <f>IF(NOT(ISNUMBER($C$6)),"Fill in C6",IF(K22&lt;=$C$6,"Yes","Not yet"))</f>
         <v/>
       </c>
     </row>
@@ -1168,27 +1241,663 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Free from the Financial Intelligence class · kopkad.ng/blog. For educational purposes only. This is not financial advice.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>With Snowball, we keep it rolling.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="C4">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(C4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>ISNUMBER(C5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>ISNUMBER(C6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>ISNUMBER(A9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>OR(B9="Within 1 year",B9="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>ISNUMBER(C9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>ISNUMBER(D9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>ISNUMBER(E9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>OR(F9="Yes",F9="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>ISNUMBER(G9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>ISNUMBER(H9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="expression" priority="12" dxfId="0">
+      <formula>ISNUMBER(A10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>OR(B10="Within 1 year",B10="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" priority="14" dxfId="0">
+      <formula>ISNUMBER(C10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="expression" priority="15" dxfId="0">
+      <formula>ISNUMBER(D10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="expression" priority="16" dxfId="0">
+      <formula>ISNUMBER(E10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="expression" priority="17" dxfId="0">
+      <formula>OR(F10="Yes",F10="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="expression" priority="18" dxfId="0">
+      <formula>ISNUMBER(G10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="expression" priority="19" dxfId="0">
+      <formula>ISNUMBER(H10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="20" dxfId="0">
+      <formula>ISNUMBER(A11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" priority="21" dxfId="0">
+      <formula>OR(B11="Within 1 year",B11="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="expression" priority="22" dxfId="0">
+      <formula>ISNUMBER(C11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="expression" priority="23" dxfId="0">
+      <formula>ISNUMBER(D11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="expression" priority="24" dxfId="0">
+      <formula>ISNUMBER(E11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="expression" priority="25" dxfId="0">
+      <formula>OR(F11="Yes",F11="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="expression" priority="26" dxfId="0">
+      <formula>ISNUMBER(G11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="expression" priority="27" dxfId="0">
+      <formula>ISNUMBER(H11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="expression" priority="28" dxfId="0">
+      <formula>ISNUMBER(A12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="29" dxfId="0">
+      <formula>OR(B12="Within 1 year",B12="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" priority="30" dxfId="0">
+      <formula>ISNUMBER(C12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="expression" priority="31" dxfId="0">
+      <formula>ISNUMBER(D12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="expression" priority="32" dxfId="0">
+      <formula>ISNUMBER(E12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="expression" priority="33" dxfId="0">
+      <formula>OR(F12="Yes",F12="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="expression" priority="34" dxfId="0">
+      <formula>ISNUMBER(G12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="expression" priority="35" dxfId="0">
+      <formula>ISNUMBER(H12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="expression" priority="36" dxfId="0">
+      <formula>ISNUMBER(A13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="37" dxfId="0">
+      <formula>OR(B13="Within 1 year",B13="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" priority="38" dxfId="0">
+      <formula>ISNUMBER(C13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="expression" priority="39" dxfId="0">
+      <formula>ISNUMBER(D13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="40" dxfId="0">
+      <formula>ISNUMBER(E13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="expression" priority="41" dxfId="0">
+      <formula>OR(F13="Yes",F13="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="expression" priority="42" dxfId="0">
+      <formula>ISNUMBER(G13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" priority="43" dxfId="0">
+      <formula>ISNUMBER(H13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="expression" priority="44" dxfId="0">
+      <formula>ISNUMBER(A14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="expression" priority="45" dxfId="0">
+      <formula>OR(B14="Within 1 year",B14="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" priority="46" dxfId="0">
+      <formula>ISNUMBER(C14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="expression" priority="47" dxfId="0">
+      <formula>ISNUMBER(D14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="expression" priority="48" dxfId="0">
+      <formula>ISNUMBER(E14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="expression" priority="49" dxfId="0">
+      <formula>OR(F14="Yes",F14="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="expression" priority="50" dxfId="0">
+      <formula>ISNUMBER(G14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="expression" priority="51" dxfId="0">
+      <formula>ISNUMBER(H14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="expression" priority="52" dxfId="0">
+      <formula>ISNUMBER(A15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="expression" priority="53" dxfId="0">
+      <formula>OR(B15="Within 1 year",B15="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="expression" priority="54" dxfId="0">
+      <formula>ISNUMBER(C15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="expression" priority="55" dxfId="0">
+      <formula>ISNUMBER(D15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="expression" priority="56" dxfId="0">
+      <formula>ISNUMBER(E15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="expression" priority="57" dxfId="0">
+      <formula>OR(F15="Yes",F15="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="expression" priority="58" dxfId="0">
+      <formula>ISNUMBER(G15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="expression" priority="59" dxfId="0">
+      <formula>ISNUMBER(H15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="expression" priority="60" dxfId="0">
+      <formula>ISNUMBER(A16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="expression" priority="61" dxfId="0">
+      <formula>OR(B16="Within 1 year",B16="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="expression" priority="62" dxfId="0">
+      <formula>ISNUMBER(C16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="expression" priority="63" dxfId="0">
+      <formula>ISNUMBER(D16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="expression" priority="64" dxfId="0">
+      <formula>ISNUMBER(E16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="expression" priority="65" dxfId="0">
+      <formula>OR(F16="Yes",F16="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="expression" priority="66" dxfId="0">
+      <formula>ISNUMBER(G16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="expression" priority="67" dxfId="0">
+      <formula>ISNUMBER(H16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="expression" priority="68" dxfId="0">
+      <formula>ISNUMBER(A17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="expression" priority="69" dxfId="0">
+      <formula>OR(B17="Within 1 year",B17="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
+    <cfRule type="expression" priority="70" dxfId="0">
+      <formula>ISNUMBER(C17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="expression" priority="71" dxfId="0">
+      <formula>ISNUMBER(D17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="72" dxfId="0">
+      <formula>ISNUMBER(E17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="expression" priority="73" dxfId="0">
+      <formula>OR(F17="Yes",F17="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="expression" priority="74" dxfId="0">
+      <formula>ISNUMBER(G17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="expression" priority="75" dxfId="0">
+      <formula>ISNUMBER(H17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="expression" priority="76" dxfId="0">
+      <formula>ISNUMBER(A18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="expression" priority="77" dxfId="0">
+      <formula>OR(B18="Within 1 year",B18="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18">
+    <cfRule type="expression" priority="78" dxfId="0">
+      <formula>ISNUMBER(C18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="expression" priority="79" dxfId="0">
+      <formula>ISNUMBER(D18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="expression" priority="80" dxfId="0">
+      <formula>ISNUMBER(E18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="expression" priority="81" dxfId="0">
+      <formula>OR(F18="Yes",F18="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="expression" priority="82" dxfId="0">
+      <formula>ISNUMBER(G18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="expression" priority="83" dxfId="0">
+      <formula>ISNUMBER(H18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="expression" priority="84" dxfId="0">
+      <formula>ISNUMBER(A19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="expression" priority="85" dxfId="0">
+      <formula>OR(B19="Within 1 year",B19="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="expression" priority="86" dxfId="0">
+      <formula>ISNUMBER(C19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="expression" priority="87" dxfId="0">
+      <formula>ISNUMBER(D19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="expression" priority="88" dxfId="0">
+      <formula>ISNUMBER(E19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="expression" priority="89" dxfId="0">
+      <formula>OR(F19="Yes",F19="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="expression" priority="90" dxfId="0">
+      <formula>ISNUMBER(G19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="expression" priority="91" dxfId="0">
+      <formula>ISNUMBER(H19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="expression" priority="92" dxfId="0">
+      <formula>ISNUMBER(A20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="expression" priority="93" dxfId="0">
+      <formula>OR(B20="Within 1 year",B20="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20">
+    <cfRule type="expression" priority="94" dxfId="0">
+      <formula>ISNUMBER(C20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="expression" priority="95" dxfId="0">
+      <formula>ISNUMBER(D20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="96" dxfId="0">
+      <formula>ISNUMBER(E20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="expression" priority="97" dxfId="0">
+      <formula>OR(F20="Yes",F20="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="expression" priority="98" dxfId="0">
+      <formula>ISNUMBER(G20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="expression" priority="99" dxfId="0">
+      <formula>ISNUMBER(H20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="99">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Rising prices" prompt="How fast prices rise each year. Start with 15%; change it if the latest inflation figure is different."/>
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Buffer" prompt="Extra added to every goal for surprises. 10% is a good start."/>
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Monthly saving" prompt="Your monthly surplus: money in minus money out, from your Money Map."/>
+    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
       <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
     </dataValidation>
-    <dataValidation sqref="F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
+    <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1218,24 +1927,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>EXAMPLE: Esther's goals</t>
         </is>
       </c>
-      <c r="B1" s="24" t="n"/>
-      <c r="C1" s="24" t="n"/>
-      <c r="D1" s="24" t="n"/>
-      <c r="E1" s="24" t="n"/>
-      <c r="F1" s="24" t="n"/>
-      <c r="G1" s="24" t="n"/>
-      <c r="H1" s="24" t="n"/>
-      <c r="I1" s="24" t="n"/>
-      <c r="J1" s="24" t="n"/>
-      <c r="K1" s="24" t="n"/>
+      <c r="B1" s="29" t="n"/>
+      <c r="C1" s="29" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>An example to show what a finished planner looks like. Fill in your own on the "My goals" tab.</t>
         </is>
@@ -1277,7 +1986,7 @@
           <t>What I can save each month</t>
         </is>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="21" t="n">
         <v>160000</v>
       </c>
       <c r="D6" s="9" t="inlineStr">
@@ -1344,420 +2053,420 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Starter emergency fund</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="31" t="inlineStr">
         <is>
           <t>Within 1 year</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="21" t="n">
         <v>150000</v>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G9" s="10" t="n">
+      <c r="G9" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="n">
+      <c r="H9" s="21" t="n">
         <v>30000</v>
       </c>
-      <c r="I9" s="15">
-        <f>IF(E9="","",IF(F9="Yes",E9+G9,(E9*(1+$C$4)^C9+G9)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="15">
-        <f>IF(I9="","",MAX(0,I9-H9))</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
-        <f>IF(OR(J9="",C9=""),"",IF(C9&lt;=0,J9,J9/(C9*12)))</f>
+      <c r="I9" s="16">
+        <f>IF(NOT(ISNUMBER(E9)),"",IF(F9="Yes",E9+N(G9),(E9*(1+$C$4)^N(C9)+N(G9))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J9" s="16">
+        <f>IF(I9="","",MAX(0,I9-N(H9)))</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>IF(OR(J9="",NOT(ISNUMBER(C9))),"",IF(C9&lt;=0,J9,J9/(C9*12)))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Rent (amount agreed with landlord)</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="31" t="inlineStr">
         <is>
           <t>Within 1 year</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="19" t="n">
         <v>0.67</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="21" t="n">
         <v>600000</v>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="21" t="n">
         <v>120000</v>
       </c>
-      <c r="I10" s="15">
-        <f>IF(E10="","",IF(F10="Yes",E10+G10,(E10*(1+$C$4)^C10+G10)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J10" s="15">
-        <f>IF(I10="","",MAX(0,I10-H10))</f>
-        <v/>
-      </c>
-      <c r="K10" s="16">
-        <f>IF(OR(J10="",C10=""),"",IF(C10&lt;=0,J10,J10/(C10*12)))</f>
+      <c r="I10" s="16">
+        <f>IF(NOT(ISNUMBER(E10)),"",IF(F10="Yes",E10+N(G10),(E10*(1+$C$4)^N(C10)+N(G10))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J10" s="16">
+        <f>IF(I10="","",MAX(0,I10-N(H10)))</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>IF(OR(J10="",NOT(ISNUMBER(C10))),"",IF(C10&lt;=0,J10,J10/(C10*12)))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Sewing machines for the business</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="31" t="inlineStr">
         <is>
           <t>1–5 years</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="21" t="n">
         <v>900000</v>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="21" t="n">
         <v>60000</v>
       </c>
-      <c r="H11" s="10" t="n">
+      <c r="H11" s="21" t="n">
         <v>200000</v>
       </c>
-      <c r="I11" s="15">
-        <f>IF(E11="","",IF(F11="Yes",E11+G11,(E11*(1+$C$4)^C11+G11)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="15">
-        <f>IF(I11="","",MAX(0,I11-H11))</f>
-        <v/>
-      </c>
-      <c r="K11" s="16">
-        <f>IF(OR(J11="",C11=""),"",IF(C11&lt;=0,J11,J11/(C11*12)))</f>
+      <c r="I11" s="16">
+        <f>IF(NOT(ISNUMBER(E11)),"",IF(F11="Yes",E11+N(G11),(E11*(1+$C$4)^N(C11)+N(G11))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J11" s="16">
+        <f>IF(I11="","",MAX(0,I11-N(H11)))</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>IF(OR(J11="",NOT(ISNUMBER(C11))),"",IF(C11&lt;=0,J11,J11/(C11*12)))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Land deposit</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
         <is>
           <t>5–10 years</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="21" t="n">
         <v>3000000</v>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="21" t="n">
         <v>250000</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="15">
-        <f>IF(E12="","",IF(F12="Yes",E12+G12,(E12*(1+$C$4)^C12+G12)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="15">
-        <f>IF(I12="","",MAX(0,I12-H12))</f>
-        <v/>
-      </c>
-      <c r="K12" s="16">
-        <f>IF(OR(J12="",C12=""),"",IF(C12&lt;=0,J12,J12/(C12*12)))</f>
+      <c r="I12" s="16">
+        <f>IF(NOT(ISNUMBER(E12)),"",IF(F12="Yes",E12+N(G12),(E12*(1+$C$4)^N(C12)+N(G12))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J12" s="16">
+        <f>IF(I12="","",MAX(0,I12-N(H12)))</f>
+        <v/>
+      </c>
+      <c r="K12" s="17">
+        <f>IF(OR(J12="",NOT(ISNUMBER(C12))),"",IF(C12&lt;=0,J12,J12/(C12*12)))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Children's university (first year)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>10–20 years</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G13" s="10" t="n">
+      <c r="G13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="15">
-        <f>IF(E13="","",IF(F13="Yes",E13+G13,(E13*(1+$C$4)^C13+G13)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="15">
-        <f>IF(I13="","",MAX(0,I13-H13))</f>
-        <v/>
-      </c>
-      <c r="K13" s="16">
-        <f>IF(OR(J13="",C13=""),"",IF(C13&lt;=0,J13,J13/(C13*12)))</f>
+      <c r="I13" s="16">
+        <f>IF(NOT(ISNUMBER(E13)),"",IF(F13="Yes",E13+N(G13),(E13*(1+$C$4)^N(C13)+N(G13))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J13" s="16">
+        <f>IF(I13="","",MAX(0,I13-N(H13)))</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>IF(OR(J13="",NOT(ISNUMBER(C13))),"",IF(C13&lt;=0,J13,J13/(C13*12)))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="10" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="15">
-        <f>IF(E14="","",IF(F14="Yes",E14+G14,(E14*(1+$C$4)^C14+G14)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J14" s="15">
-        <f>IF(I14="","",MAX(0,I14-H14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="16">
-        <f>IF(OR(J14="",C14=""),"",IF(C14&lt;=0,J14,J14/(C14*12)))</f>
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="13" t="inlineStr"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="13" t="inlineStr"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="16">
+        <f>IF(NOT(ISNUMBER(E14)),"",IF(F14="Yes",E14+N(G14),(E14*(1+$C$4)^N(C14)+N(G14))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J14" s="16">
+        <f>IF(I14="","",MAX(0,I14-N(H14)))</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>IF(OR(J14="",NOT(ISNUMBER(C14))),"",IF(C14&lt;=0,J14,J14/(C14*12)))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="13" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="14" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-      <c r="I15" s="15">
-        <f>IF(E15="","",IF(F15="Yes",E15+G15,(E15*(1+$C$4)^C15+G15)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J15" s="15">
-        <f>IF(I15="","",MAX(0,I15-H15))</f>
-        <v/>
-      </c>
-      <c r="K15" s="16">
-        <f>IF(OR(J15="",C15=""),"",IF(C15&lt;=0,J15,J15/(C15*12)))</f>
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="13" t="inlineStr"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="13" t="inlineStr"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="16">
+        <f>IF(NOT(ISNUMBER(E15)),"",IF(F15="Yes",E15+N(G15),(E15*(1+$C$4)^N(C15)+N(G15))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J15" s="16">
+        <f>IF(I15="","",MAX(0,I15-N(H15)))</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>IF(OR(J15="",NOT(ISNUMBER(C15))),"",IF(C15&lt;=0,J15,J15/(C15*12)))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="10" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n"/>
-      <c r="I16" s="15">
-        <f>IF(E16="","",IF(F16="Yes",E16+G16,(E16*(1+$C$4)^C16+G16)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="15">
-        <f>IF(I16="","",MAX(0,I16-H16))</f>
-        <v/>
-      </c>
-      <c r="K16" s="16">
-        <f>IF(OR(J16="",C16=""),"",IF(C16&lt;=0,J16,J16/(C16*12)))</f>
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="13" t="inlineStr"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="21" t="n"/>
+      <c r="H16" s="21" t="n"/>
+      <c r="I16" s="16">
+        <f>IF(NOT(ISNUMBER(E16)),"",IF(F16="Yes",E16+N(G16),(E16*(1+$C$4)^N(C16)+N(G16))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J16" s="16">
+        <f>IF(I16="","",MAX(0,I16-N(H16)))</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>IF(OR(J16="",NOT(ISNUMBER(C16))),"",IF(C16&lt;=0,J16,J16/(C16*12)))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="10" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="10" t="n"/>
-      <c r="I17" s="15">
-        <f>IF(E17="","",IF(F17="Yes",E17+G17,(E17*(1+$C$4)^C17+G17)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="15">
-        <f>IF(I17="","",MAX(0,I17-H17))</f>
-        <v/>
-      </c>
-      <c r="K17" s="16">
-        <f>IF(OR(J17="",C17=""),"",IF(C17&lt;=0,J17,J17/(C17*12)))</f>
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="13" t="inlineStr"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="21" t="n"/>
+      <c r="F17" s="13" t="inlineStr"/>
+      <c r="G17" s="21" t="n"/>
+      <c r="H17" s="21" t="n"/>
+      <c r="I17" s="16">
+        <f>IF(NOT(ISNUMBER(E17)),"",IF(F17="Yes",E17+N(G17),(E17*(1+$C$4)^N(C17)+N(G17))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J17" s="16">
+        <f>IF(I17="","",MAX(0,I17-N(H17)))</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>IF(OR(J17="",NOT(ISNUMBER(C17))),"",IF(C17&lt;=0,J17,J17/(C17*12)))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="15">
-        <f>IF(E18="","",IF(F18="Yes",E18+G18,(E18*(1+$C$4)^C18+G18)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J18" s="15">
-        <f>IF(I18="","",MAX(0,I18-H18))</f>
-        <v/>
-      </c>
-      <c r="K18" s="16">
-        <f>IF(OR(J18="",C18=""),"",IF(C18&lt;=0,J18,J18/(C18*12)))</f>
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="13" t="inlineStr"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="13" t="inlineStr"/>
+      <c r="G18" s="21" t="n"/>
+      <c r="H18" s="21" t="n"/>
+      <c r="I18" s="16">
+        <f>IF(NOT(ISNUMBER(E18)),"",IF(F18="Yes",E18+N(G18),(E18*(1+$C$4)^N(C18)+N(G18))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J18" s="16">
+        <f>IF(I18="","",MAX(0,I18-N(H18)))</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF(OR(J18="",NOT(ISNUMBER(C18))),"",IF(C18&lt;=0,J18,J18/(C18*12)))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="15">
-        <f>IF(E19="","",IF(F19="Yes",E19+G19,(E19*(1+$C$4)^C19+G19)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J19" s="15">
-        <f>IF(I19="","",MAX(0,I19-H19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="16">
-        <f>IF(OR(J19="",C19=""),"",IF(C19&lt;=0,J19,J19/(C19*12)))</f>
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="13" t="inlineStr"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="21" t="n"/>
+      <c r="F19" s="13" t="inlineStr"/>
+      <c r="G19" s="21" t="n"/>
+      <c r="H19" s="21" t="n"/>
+      <c r="I19" s="16">
+        <f>IF(NOT(ISNUMBER(E19)),"",IF(F19="Yes",E19+N(G19),(E19*(1+$C$4)^N(C19)+N(G19))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J19" s="16">
+        <f>IF(I19="","",MAX(0,I19-N(H19)))</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>IF(OR(J19="",NOT(ISNUMBER(C19))),"",IF(C19&lt;=0,J19,J19/(C19*12)))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="10" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="15">
-        <f>IF(E20="","",IF(F20="Yes",E20+G20,(E20*(1+$C$4)^C20+G20)*(1+$C$5)))</f>
-        <v/>
-      </c>
-      <c r="J20" s="15">
-        <f>IF(I20="","",MAX(0,I20-H20))</f>
-        <v/>
-      </c>
-      <c r="K20" s="16">
-        <f>IF(OR(J20="",C20=""),"",IF(C20&lt;=0,J20,J20/(C20*12)))</f>
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="13" t="inlineStr"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="13" t="inlineStr"/>
+      <c r="G20" s="21" t="n"/>
+      <c r="H20" s="21" t="n"/>
+      <c r="I20" s="16">
+        <f>IF(NOT(ISNUMBER(E20)),"",IF(F20="Yes",E20+N(G20),(E20*(1+$C$4)^N(C20)+N(G20))*(1+$C$5)))</f>
+        <v/>
+      </c>
+      <c r="J20" s="16">
+        <f>IF(I20="","",MAX(0,I20-N(H20)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>IF(OR(J20="",NOT(ISNUMBER(C20))),"",IF(C20&lt;=0,J20,J20/(C20*12)))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>Total needed each month for all goals</t>
         </is>
       </c>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="18" t="n"/>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="19">
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="24">
         <f>SUM(K9:K20)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Can I afford all of them?</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>If "Not yet": give each goal a priority, fund the top ones first, move a date later, or start smaller.</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="18" t="n"/>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="17">
-        <f>IF($C$6="","Fill in C6",IF(K22&lt;=$C$6,"Yes","Not yet"))</f>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="22">
+        <f>IF(NOT(ISNUMBER($C$6)),"Fill in C6",IF(K22&lt;=$C$6,"Yes","Not yet"))</f>
         <v/>
       </c>
     </row>
@@ -1769,27 +2478,663 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Free from the Financial Intelligence class · kopkad.ng/blog. For educational purposes only. This is not financial advice.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>With Snowball, we keep it rolling.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <conditionalFormatting sqref="C4">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>ISNUMBER(C4)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>ISNUMBER(C5)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" priority="3" dxfId="0">
+      <formula>ISNUMBER(C6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="expression" priority="4" dxfId="0">
+      <formula>ISNUMBER(A9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>OR(B9="Within 1 year",B9="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>ISNUMBER(C9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="expression" priority="7" dxfId="0">
+      <formula>ISNUMBER(D9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="expression" priority="8" dxfId="0">
+      <formula>ISNUMBER(E9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F9">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>OR(F9="Yes",F9="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>ISNUMBER(G9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9">
+    <cfRule type="expression" priority="11" dxfId="0">
+      <formula>ISNUMBER(H9)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="expression" priority="12" dxfId="0">
+      <formula>ISNUMBER(A10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>OR(B10="Within 1 year",B10="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" priority="14" dxfId="0">
+      <formula>ISNUMBER(C10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="expression" priority="15" dxfId="0">
+      <formula>ISNUMBER(D10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="expression" priority="16" dxfId="0">
+      <formula>ISNUMBER(E10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="expression" priority="17" dxfId="0">
+      <formula>OR(F10="Yes",F10="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="expression" priority="18" dxfId="0">
+      <formula>ISNUMBER(G10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H10">
+    <cfRule type="expression" priority="19" dxfId="0">
+      <formula>ISNUMBER(H10)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="expression" priority="20" dxfId="0">
+      <formula>ISNUMBER(A11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="expression" priority="21" dxfId="0">
+      <formula>OR(B11="Within 1 year",B11="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="expression" priority="22" dxfId="0">
+      <formula>ISNUMBER(C11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="expression" priority="23" dxfId="0">
+      <formula>ISNUMBER(D11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="expression" priority="24" dxfId="0">
+      <formula>ISNUMBER(E11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11">
+    <cfRule type="expression" priority="25" dxfId="0">
+      <formula>OR(F11="Yes",F11="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11">
+    <cfRule type="expression" priority="26" dxfId="0">
+      <formula>ISNUMBER(G11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11">
+    <cfRule type="expression" priority="27" dxfId="0">
+      <formula>ISNUMBER(H11)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="expression" priority="28" dxfId="0">
+      <formula>ISNUMBER(A12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B12">
+    <cfRule type="expression" priority="29" dxfId="0">
+      <formula>OR(B12="Within 1 year",B12="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" priority="30" dxfId="0">
+      <formula>ISNUMBER(C12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="expression" priority="31" dxfId="0">
+      <formula>ISNUMBER(D12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="expression" priority="32" dxfId="0">
+      <formula>ISNUMBER(E12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12">
+    <cfRule type="expression" priority="33" dxfId="0">
+      <formula>OR(F12="Yes",F12="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="expression" priority="34" dxfId="0">
+      <formula>ISNUMBER(G12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H12">
+    <cfRule type="expression" priority="35" dxfId="0">
+      <formula>ISNUMBER(H12)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="expression" priority="36" dxfId="0">
+      <formula>ISNUMBER(A13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13">
+    <cfRule type="expression" priority="37" dxfId="0">
+      <formula>OR(B13="Within 1 year",B13="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" priority="38" dxfId="0">
+      <formula>ISNUMBER(C13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="expression" priority="39" dxfId="0">
+      <formula>ISNUMBER(D13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13">
+    <cfRule type="expression" priority="40" dxfId="0">
+      <formula>ISNUMBER(E13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="expression" priority="41" dxfId="0">
+      <formula>OR(F13="Yes",F13="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="expression" priority="42" dxfId="0">
+      <formula>ISNUMBER(G13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13">
+    <cfRule type="expression" priority="43" dxfId="0">
+      <formula>ISNUMBER(H13)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="expression" priority="44" dxfId="0">
+      <formula>ISNUMBER(A14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="expression" priority="45" dxfId="0">
+      <formula>OR(B14="Within 1 year",B14="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" priority="46" dxfId="0">
+      <formula>ISNUMBER(C14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="expression" priority="47" dxfId="0">
+      <formula>ISNUMBER(D14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14">
+    <cfRule type="expression" priority="48" dxfId="0">
+      <formula>ISNUMBER(E14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14">
+    <cfRule type="expression" priority="49" dxfId="0">
+      <formula>OR(F14="Yes",F14="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="expression" priority="50" dxfId="0">
+      <formula>ISNUMBER(G14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H14">
+    <cfRule type="expression" priority="51" dxfId="0">
+      <formula>ISNUMBER(H14)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="expression" priority="52" dxfId="0">
+      <formula>ISNUMBER(A15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="expression" priority="53" dxfId="0">
+      <formula>OR(B15="Within 1 year",B15="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="expression" priority="54" dxfId="0">
+      <formula>ISNUMBER(C15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="expression" priority="55" dxfId="0">
+      <formula>ISNUMBER(D15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E15">
+    <cfRule type="expression" priority="56" dxfId="0">
+      <formula>ISNUMBER(E15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="expression" priority="57" dxfId="0">
+      <formula>OR(F15="Yes",F15="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="expression" priority="58" dxfId="0">
+      <formula>ISNUMBER(G15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H15">
+    <cfRule type="expression" priority="59" dxfId="0">
+      <formula>ISNUMBER(H15)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="expression" priority="60" dxfId="0">
+      <formula>ISNUMBER(A16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16">
+    <cfRule type="expression" priority="61" dxfId="0">
+      <formula>OR(B16="Within 1 year",B16="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="expression" priority="62" dxfId="0">
+      <formula>ISNUMBER(C16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="expression" priority="63" dxfId="0">
+      <formula>ISNUMBER(D16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E16">
+    <cfRule type="expression" priority="64" dxfId="0">
+      <formula>ISNUMBER(E16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16">
+    <cfRule type="expression" priority="65" dxfId="0">
+      <formula>OR(F16="Yes",F16="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G16">
+    <cfRule type="expression" priority="66" dxfId="0">
+      <formula>ISNUMBER(G16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16">
+    <cfRule type="expression" priority="67" dxfId="0">
+      <formula>ISNUMBER(H16)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="expression" priority="68" dxfId="0">
+      <formula>ISNUMBER(A17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17">
+    <cfRule type="expression" priority="69" dxfId="0">
+      <formula>OR(B17="Within 1 year",B17="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C17">
+    <cfRule type="expression" priority="70" dxfId="0">
+      <formula>ISNUMBER(C17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17">
+    <cfRule type="expression" priority="71" dxfId="0">
+      <formula>ISNUMBER(D17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17">
+    <cfRule type="expression" priority="72" dxfId="0">
+      <formula>ISNUMBER(E17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17">
+    <cfRule type="expression" priority="73" dxfId="0">
+      <formula>OR(F17="Yes",F17="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="expression" priority="74" dxfId="0">
+      <formula>ISNUMBER(G17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H17">
+    <cfRule type="expression" priority="75" dxfId="0">
+      <formula>ISNUMBER(H17)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="expression" priority="76" dxfId="0">
+      <formula>ISNUMBER(A18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="expression" priority="77" dxfId="0">
+      <formula>OR(B18="Within 1 year",B18="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C18">
+    <cfRule type="expression" priority="78" dxfId="0">
+      <formula>ISNUMBER(C18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18">
+    <cfRule type="expression" priority="79" dxfId="0">
+      <formula>ISNUMBER(D18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E18">
+    <cfRule type="expression" priority="80" dxfId="0">
+      <formula>ISNUMBER(E18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F18">
+    <cfRule type="expression" priority="81" dxfId="0">
+      <formula>OR(F18="Yes",F18="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="expression" priority="82" dxfId="0">
+      <formula>ISNUMBER(G18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="expression" priority="83" dxfId="0">
+      <formula>ISNUMBER(H18)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="expression" priority="84" dxfId="0">
+      <formula>ISNUMBER(A19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19">
+    <cfRule type="expression" priority="85" dxfId="0">
+      <formula>OR(B19="Within 1 year",B19="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C19">
+    <cfRule type="expression" priority="86" dxfId="0">
+      <formula>ISNUMBER(C19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="expression" priority="87" dxfId="0">
+      <formula>ISNUMBER(D19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="expression" priority="88" dxfId="0">
+      <formula>ISNUMBER(E19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="expression" priority="89" dxfId="0">
+      <formula>OR(F19="Yes",F19="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="expression" priority="90" dxfId="0">
+      <formula>ISNUMBER(G19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H19">
+    <cfRule type="expression" priority="91" dxfId="0">
+      <formula>ISNUMBER(H19)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="expression" priority="92" dxfId="0">
+      <formula>ISNUMBER(A20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="expression" priority="93" dxfId="0">
+      <formula>OR(B20="Within 1 year",B20="20+ years")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20">
+    <cfRule type="expression" priority="94" dxfId="0">
+      <formula>ISNUMBER(C20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="expression" priority="95" dxfId="0">
+      <formula>ISNUMBER(D20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20">
+    <cfRule type="expression" priority="96" dxfId="0">
+      <formula>ISNUMBER(E20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="expression" priority="97" dxfId="0">
+      <formula>OR(F20="Yes",F20="No")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="expression" priority="98" dxfId="0">
+      <formula>ISNUMBER(G20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H20">
+    <cfRule type="expression" priority="99" dxfId="0">
+      <formula>ISNUMBER(H20)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="99">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Rising prices" prompt="How fast prices rise each year. Start with 15%; change it if the latest inflation figure is different."/>
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Buffer" prompt="Extra added to every goal for surprises. 10% is a good start."/>
+    <dataValidation sqref="C6" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Monthly saving" prompt="Your monthly surplus: money in minus money out, from your Money Map."/>
+    <dataValidation sqref="A9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
       <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
     </dataValidation>
-    <dataValidation sqref="F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F9" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
+    <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F10" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H10" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H11" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F12" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F14" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F15" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H15" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F17" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
+    <dataValidation sqref="A20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Goal" prompt="What the goal is, in a few words."/>
+    <dataValidation sqref="B20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="How far away the goal is." type="list">
+      <formula1>"Within 1 year,1–5 years,5–10 years,10–20 years,20+ years"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Years from now" prompt="How long until you need the money. 6 months = 0.5, 8 months = 0.67, 2 years = 2."/>
+    <dataValidation sqref="D20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Priority" prompt="1 for the goal that comes first. Safety buffer, then expensive debt, then goals by date."/>
+    <dataValidation sqref="E20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Today's price" prompt="What it costs today. Get a real quote if you can."/>
+    <dataValidation sqref="F20" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose one of the options in the list." promptTitle="Choose one" prompt="Yes if the price is already agreed for when you need it, like an agreed rent. Then no rising prices or buffer are added." type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Extras" prompt="Delivery, installation, registration, legal or agent fees."/>
+    <dataValidation sqref="H20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Already saved" prompt="What you have already put aside towards this goal."/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
